--- a/tame_output/ON/bt/strategyON_20240201.xlsx
+++ b/tame_output/ON/bt/strategyON_20240201.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-0.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.5%</t>
+          <t>451.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.9%</t>
+          <t>128.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,16 +1400,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>2024-01-31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1859"/>
+  <dimension ref="A1:G1860"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30487093613488</v>
+        <v>3.305316798207816</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44318,6 +44318,29 @@
       </c>
       <c r="G1859" t="n">
         <v>4.475064780938972</v>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" s="2" t="n">
+        <v>45322</v>
+      </c>
+      <c r="B1860" t="n">
+        <v>3.283988034426075</v>
+      </c>
+      <c r="C1860" t="n">
+        <v>3.112356309032875</v>
+      </c>
+      <c r="D1860" t="n">
+        <v>1.64347466511187</v>
+      </c>
+      <c r="E1860" t="n">
+        <v>3.769389750763875</v>
+      </c>
+      <c r="F1860" t="n">
+        <v>2.257489958303713</v>
+      </c>
+      <c r="G1860" t="n">
+        <v>4.466850284015102</v>
       </c>
     </row>
   </sheetData>
